--- a/test_single.xlsx
+++ b/test_single.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Contacts" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,12 +431,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Test User</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>+919495247289</t>
+          <t>9495247289</t>
         </is>
       </c>
     </row>
